--- a/information_request_forms/016_rf_shielding_product_inquiry_form--information_request_forms.xlsx
+++ b/information_request_forms/016_rf_shielding_product_inquiry_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2321,29 +2321,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>puerto_rico</t>
+          <t>virgin_islands</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>product_inquiry_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>virgin_islands</t>
+          <t>rf_product_inquiry_form</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Virgin Islands</t>
+          <t>RF Product Inquiry Form</t>
         </is>
       </c>
     </row>
@@ -2355,29 +2355,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>rf_product_inquiry_form</t>
+          <t>rf_product_inquiry_form_-_custom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>RF Product Inquiry Form</t>
+          <t>RF Product Inquiry Form - Custom</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>product_inquiry_choices</t>
+          <t>assigned_engineer_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>rf_product_inquiry_form_-_custom</t>
+          <t>engineer1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RF Product Inquiry Form - Custom</t>
+          <t>Engineer1</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>engineer1</t>
+          <t>engineer2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Engineer1</t>
+          <t>Engineer2</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2406,10 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>engineer2</t>
+          <t>engineer3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
-        <is>
-          <t>Engineer2</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>assigned_engineer_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>engineer3</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
         <is>
           <t>Engineer3</t>
         </is>
